--- a/files/REG_Policy_Peer_Regulator_Scan.xlsx
+++ b/files/REG_Policy_Peer_Regulator_Scan.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer scan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Themes summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,19 +26,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -52,12 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,30 +79,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,400 +489,907 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peer regulator scan — recent instruments</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Peer</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Instrument</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Theme</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>REG Policy Peer Regulator Scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source file: REG_Policy_Peer_Regulator_Scan.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Peer A</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Guidelines on private-credit licensing</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Private credit</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Peer A</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Consultation on retail-feeder cooling-off</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Investor protection</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Consultation</t>
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 01</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>244419.23</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Peer B</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Notice on stablecoin custody</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Crypto-adjacent</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Final</t>
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 02</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>270044.7</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Peer B</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Cross-border recognition MoU</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Cross-border</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Signed</t>
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 03</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>24528.74</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Peer C</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Tiered fund-manager licensing</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Fund management</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Final</t>
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 04</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>235874.21</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Peer C</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Consultation on AI-assisted advice</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Conduct</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Consultation</t>
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 05</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>222085.31</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Peer D</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Code on social-media solicitation</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Conduct</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Final</t>
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 06</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>276208.7</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Under review</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Peer D</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Sandbox for tokenised debt</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Innovation</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 07</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>409966.88</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 08</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>357214.16</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 09</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>226349.9</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 10</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>360680.98</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 11</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>15678.66</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 12</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>22433.67</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 13</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>45889.84</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 14</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>367998.81</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 15</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>71332.57000000001</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 16</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>338240.12</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 17</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>122223.13</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 18</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>265504.39</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 19</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>174149.78</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 20</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>195394.22</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 21</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>363080.52</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 22</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>244075.76</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 23</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>270744.94</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 24</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>247193.67</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 25</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>320140.59</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 26</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>427102.62</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 27</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>79807.12</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 28</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>155758.41</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 29</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>479513.45</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>REG Policy Peer Regulator Scan — line item 30</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>259362.99</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Under review</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Themes seen across peers</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Theme</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Peers active</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Implication for Zava</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tiered licensing for fund managers</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Peer A, C</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Inform our own private-credit tiering</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Cooling-off for retail feeders</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Peer A, D</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Consider in policy refresh</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Stablecoin custody framework</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Peer B</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Watch but defer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Social-media solicitation enforcement</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Peer D</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Strengthen our anti-scam playbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Tokenised debt sandbox</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Peer D</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Scout for participation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
